--- a/Total_Oxide_Calculations/Oxides_Julia.xlsx
+++ b/Total_Oxide_Calculations/Oxides_Julia.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unibe365-my.sharepoint.com/personal/sebastian_stumpf_unibe_ch/Documents/PhD/ICP-Base/ICP-Base_dev/Total_Mass_Calculations/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unibe365-my.sharepoint.com/personal/sebastian_stumpf_unibe_ch/Documents/PhD/ICP-Base/ICP-Base_dev/Total_Oxide_Calculations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="172" documentId="11_AD4DB114E441178AC67DF4EAB656CEA0693EDF1D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA656271-CA40-4095-95B8-58EDD17B10BB}"/>
+  <xr:revisionPtr revIDLastSave="174" documentId="11_AD4DB114E441178AC67DF4EAB656CEA0693EDF1D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1782993-D608-4FF4-ADD0-FCC4F7D1FDE1}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="195" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
   <si>
     <t>SiO2</t>
   </si>
@@ -130,6 +130,15 @@
   </si>
   <si>
     <t>Yes</t>
+  </si>
+  <si>
+    <t>Ni</t>
+  </si>
+  <si>
+    <t>NiO</t>
+  </si>
+  <si>
+    <t>Ni62</t>
   </si>
 </sst>
 </file>
@@ -188,10 +197,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -457,7 +462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -651,6 +656,23 @@
         <v>34</v>
       </c>
     </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1.2726</v>
+      </c>
+      <c r="D12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
